--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12961,7 +12961,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14383,7 +14383,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14462,7 +14462,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15963,7 +15963,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17969,7 +17969,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20356,7 +20356,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20587,7 +20587,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20664,7 +20664,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20818,7 +20818,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21280,7 +21280,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21511,7 +21511,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21742,7 +21742,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21819,7 +21819,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22050,7 +22050,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22204,7 +22204,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22512,7 +22512,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22589,7 +22589,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22666,7 +22666,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22743,7 +22743,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22820,7 +22820,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23359,7 +23359,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23436,7 +23436,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23513,7 +23513,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23667,7 +23667,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23744,7 +23744,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23821,7 +23821,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23975,7 +23975,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24052,7 +24052,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24283,7 +24283,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24360,7 +24360,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24437,7 +24437,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24514,7 +24514,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24591,7 +24591,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24668,7 +24668,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24745,7 +24745,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24822,7 +24822,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25053,7 +25053,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25207,7 +25207,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25515,7 +25515,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25592,7 +25592,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25746,7 +25746,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25823,7 +25823,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25900,7 +25900,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26285,7 +26285,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26362,7 +26362,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36316,7 +36316,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36474,7 +36474,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36553,7 +36553,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36711,7 +36711,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36790,7 +36790,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37027,7 +37027,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37106,7 +37106,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37185,7 +37185,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37264,7 +37264,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37343,7 +37343,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37422,7 +37422,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37501,7 +37501,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37580,7 +37580,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37659,7 +37659,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37738,7 +37738,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37817,7 +37817,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37896,7 +37896,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37975,7 +37975,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38054,7 +38054,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38133,7 +38133,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38212,7 +38212,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38370,7 +38370,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38449,7 +38449,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38528,7 +38528,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38607,7 +38607,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38686,7 +38686,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38765,7 +38765,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38844,7 +38844,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38923,7 +38923,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39002,7 +39002,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39081,7 +39081,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39160,7 +39160,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39239,7 +39239,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39318,7 +39318,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39397,7 +39397,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39476,7 +39476,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39634,7 +39634,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39792,7 +39792,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39871,7 +39871,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39950,7 +39950,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40029,7 +40029,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40108,7 +40108,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40187,7 +40187,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40266,7 +40266,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40345,7 +40345,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40424,7 +40424,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40503,7 +40503,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40582,7 +40582,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40661,7 +40661,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40740,7 +40740,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40819,7 +40819,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40898,7 +40898,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40977,7 +40977,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41135,7 +41135,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41214,7 +41214,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41293,7 +41293,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41372,7 +41372,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41451,7 +41451,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41530,7 +41530,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41609,7 +41609,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41688,7 +41688,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41767,7 +41767,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41846,7 +41846,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41925,7 +41925,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42004,7 +42004,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42083,7 +42083,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42162,7 +42162,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42241,7 +42241,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42478,7 +42478,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42557,7 +42557,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42636,7 +42636,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42715,7 +42715,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42794,7 +42794,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42873,7 +42873,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42952,7 +42952,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43031,7 +43031,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43110,7 +43110,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43189,7 +43189,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43268,7 +43268,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43347,7 +43347,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43426,7 +43426,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43505,7 +43505,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43584,7 +43584,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43663,7 +43663,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43742,7 +43742,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43821,7 +43821,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43900,7 +43900,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43979,7 +43979,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44137,7 +44137,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44216,7 +44216,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44295,7 +44295,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44374,7 +44374,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44453,7 +44453,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44532,7 +44532,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44611,7 +44611,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44690,7 +44690,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44769,7 +44769,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44848,7 +44848,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44927,7 +44927,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45006,7 +45006,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45085,7 +45085,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45164,7 +45164,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45243,7 +45243,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45322,7 +45322,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45401,7 +45401,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45480,7 +45480,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45559,7 +45559,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45638,7 +45638,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45717,7 +45717,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45796,7 +45796,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45954,7 +45954,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46033,7 +46033,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46112,7 +46112,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46191,7 +46191,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46270,7 +46270,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46349,7 +46349,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46428,7 +46428,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46507,7 +46507,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46586,7 +46586,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46665,7 +46665,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46744,7 +46744,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46823,7 +46823,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46902,7 +46902,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46981,7 +46981,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47060,7 +47060,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47139,7 +47139,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47218,7 +47218,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47303,7 +47303,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12961,7 +12961,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14383,7 +14383,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14462,7 +14462,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15963,7 +15963,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17969,7 +17969,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20356,7 +20356,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20587,7 +20587,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20664,7 +20664,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20818,7 +20818,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21280,7 +21280,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21511,7 +21511,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21742,7 +21742,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21819,7 +21819,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22050,7 +22050,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22204,7 +22204,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22512,7 +22512,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22589,7 +22589,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22666,7 +22666,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22743,7 +22743,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22820,7 +22820,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23359,7 +23359,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23436,7 +23436,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23513,7 +23513,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23667,7 +23667,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23744,7 +23744,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23821,7 +23821,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23975,7 +23975,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24052,7 +24052,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24283,7 +24283,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24360,7 +24360,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24437,7 +24437,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24514,7 +24514,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24591,7 +24591,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24668,7 +24668,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24745,7 +24745,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24822,7 +24822,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25053,7 +25053,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25207,7 +25207,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25515,7 +25515,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25592,7 +25592,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25746,7 +25746,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25823,7 +25823,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25900,7 +25900,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26285,7 +26285,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26362,7 +26362,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36316,7 +36316,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36474,7 +36474,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36553,7 +36553,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36711,7 +36711,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36790,7 +36790,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37027,7 +37027,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37106,7 +37106,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37185,7 +37185,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37264,7 +37264,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37343,7 +37343,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37422,7 +37422,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37501,7 +37501,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37580,7 +37580,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37659,7 +37659,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37738,7 +37738,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37817,7 +37817,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37896,7 +37896,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37975,7 +37975,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38054,7 +38054,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38133,7 +38133,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38212,7 +38212,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38370,7 +38370,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38449,7 +38449,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38528,7 +38528,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38607,7 +38607,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38686,7 +38686,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38765,7 +38765,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38844,7 +38844,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38923,7 +38923,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39002,7 +39002,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39081,7 +39081,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39160,7 +39160,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39239,7 +39239,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39318,7 +39318,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39397,7 +39397,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39476,7 +39476,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39634,7 +39634,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39792,7 +39792,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39871,7 +39871,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39950,7 +39950,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40029,7 +40029,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40108,7 +40108,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40187,7 +40187,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40266,7 +40266,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40345,7 +40345,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40424,7 +40424,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40503,7 +40503,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40582,7 +40582,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40661,7 +40661,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40740,7 +40740,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40819,7 +40819,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40898,7 +40898,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40977,7 +40977,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41135,7 +41135,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41214,7 +41214,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41293,7 +41293,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41372,7 +41372,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41451,7 +41451,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41530,7 +41530,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41609,7 +41609,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41688,7 +41688,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41767,7 +41767,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41846,7 +41846,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41925,7 +41925,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42004,7 +42004,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42083,7 +42083,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42162,7 +42162,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42241,7 +42241,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42478,7 +42478,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42557,7 +42557,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42636,7 +42636,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42715,7 +42715,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42794,7 +42794,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42873,7 +42873,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42952,7 +42952,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43031,7 +43031,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43110,7 +43110,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43189,7 +43189,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43268,7 +43268,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43347,7 +43347,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43426,7 +43426,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43505,7 +43505,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43584,7 +43584,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43663,7 +43663,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43742,7 +43742,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43821,7 +43821,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43900,7 +43900,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43979,7 +43979,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44137,7 +44137,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44216,7 +44216,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44295,7 +44295,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44374,7 +44374,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44453,7 +44453,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44532,7 +44532,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44611,7 +44611,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44690,7 +44690,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44769,7 +44769,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44848,7 +44848,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44927,7 +44927,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45006,7 +45006,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45085,7 +45085,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45164,7 +45164,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45243,7 +45243,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45322,7 +45322,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45401,7 +45401,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45480,7 +45480,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45559,7 +45559,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45638,7 +45638,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45717,7 +45717,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45796,7 +45796,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45954,7 +45954,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46033,7 +46033,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46112,7 +46112,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46191,7 +46191,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46270,7 +46270,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46349,7 +46349,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46428,7 +46428,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46507,7 +46507,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46586,7 +46586,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46665,7 +46665,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46744,7 +46744,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46823,7 +46823,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46902,7 +46902,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46981,7 +46981,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47060,7 +47060,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47139,7 +47139,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47218,7 +47218,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47303,7 +47303,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8022,7 +8022,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9049,7 +9049,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10313,7 +10313,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10467,7 +10467,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11622,7 +11622,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11855,7 +11855,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12408,7 +12408,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12961,7 +12961,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13514,7 +13514,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14383,7 +14383,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14462,7 +14462,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15252,7 +15252,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15963,7 +15963,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16121,7 +16121,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17122,7 +17122,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17199,7 +17199,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17353,7 +17353,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17969,7 +17969,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18431,7 +18431,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18739,7 +18739,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18816,7 +18816,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18970,7 +18970,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19124,7 +19124,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19432,7 +19432,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19817,7 +19817,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19894,7 +19894,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20048,7 +20048,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20202,7 +20202,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20356,7 +20356,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20587,7 +20587,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20664,7 +20664,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20741,7 +20741,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20818,7 +20818,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21280,7 +21280,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21434,7 +21434,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21511,7 +21511,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21742,7 +21742,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21819,7 +21819,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21896,7 +21896,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22050,7 +22050,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22127,7 +22127,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22204,7 +22204,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22512,7 +22512,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22589,7 +22589,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22666,7 +22666,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22743,7 +22743,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22820,7 +22820,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23359,7 +23359,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23436,7 +23436,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23513,7 +23513,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23590,7 +23590,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23667,7 +23667,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23744,7 +23744,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23821,7 +23821,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23975,7 +23975,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24052,7 +24052,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24129,7 +24129,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24283,7 +24283,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24360,7 +24360,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24437,7 +24437,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24514,7 +24514,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24591,7 +24591,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24668,7 +24668,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24745,7 +24745,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24822,7 +24822,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25053,7 +25053,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25130,7 +25130,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25207,7 +25207,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25284,7 +25284,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25361,7 +25361,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25438,7 +25438,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25515,7 +25515,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25592,7 +25592,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25669,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25746,7 +25746,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25823,7 +25823,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25900,7 +25900,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25977,7 +25977,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26285,7 +26285,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26362,7 +26362,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26599,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27310,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27468,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27547,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27784,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27863,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27942,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28021,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28179,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28337,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28416,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28574,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28811,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28969,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29285,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29443,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29522,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29680,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29759,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29838,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +29996,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30075,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30154,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30391,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30549,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30865,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30944,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31023,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31102,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31181,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31418,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31576,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31655,7 +31655,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31734,7 +31734,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -31892,7 +31892,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -31971,7 +31971,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32050,7 +32050,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32129,7 +32129,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32208,7 +32208,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32287,7 +32287,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32445,7 +32445,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32603,7 +32603,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32761,7 +32761,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -32998,7 +32998,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33156,7 +33156,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33314,7 +33314,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33393,7 +33393,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33472,7 +33472,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33551,7 +33551,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33630,7 +33630,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33709,7 +33709,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -33946,7 +33946,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34025,7 +34025,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34104,7 +34104,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34183,7 +34183,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34341,7 +34341,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34420,7 +34420,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34499,7 +34499,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34578,7 +34578,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34736,7 +34736,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -34815,7 +34815,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -34894,7 +34894,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35131,7 +35131,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35210,7 +35210,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35289,7 +35289,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35368,7 +35368,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35526,7 +35526,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35763,7 +35763,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -35921,7 +35921,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36000,7 +36000,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36079,7 +36079,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36158,7 +36158,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36316,7 +36316,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36395,7 +36395,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36474,7 +36474,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36553,7 +36553,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36632,7 +36632,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36711,7 +36711,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -36790,7 +36790,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -36869,7 +36869,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -36948,7 +36948,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37027,7 +37027,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37106,7 +37106,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37185,7 +37185,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37264,7 +37264,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37343,7 +37343,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37422,7 +37422,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37501,7 +37501,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37580,7 +37580,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37659,7 +37659,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37738,7 +37738,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37817,7 +37817,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37896,7 +37896,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37975,7 +37975,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38054,7 +38054,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38133,7 +38133,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38212,7 +38212,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38370,7 +38370,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38449,7 +38449,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38528,7 +38528,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38607,7 +38607,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38686,7 +38686,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38765,7 +38765,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38844,7 +38844,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38923,7 +38923,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39002,7 +39002,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39081,7 +39081,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39160,7 +39160,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39239,7 +39239,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39318,7 +39318,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39397,7 +39397,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39476,7 +39476,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39555,7 +39555,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39634,7 +39634,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39713,7 +39713,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39792,7 +39792,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39871,7 +39871,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39950,7 +39950,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40029,7 +40029,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40108,7 +40108,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40187,7 +40187,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40266,7 +40266,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40345,7 +40345,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40424,7 +40424,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40503,7 +40503,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40582,7 +40582,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40661,7 +40661,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40740,7 +40740,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40819,7 +40819,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40898,7 +40898,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40977,7 +40977,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41056,7 +41056,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41135,7 +41135,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41214,7 +41214,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41293,7 +41293,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41372,7 +41372,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41451,7 +41451,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41530,7 +41530,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41609,7 +41609,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41688,7 +41688,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41767,7 +41767,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41846,7 +41846,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41925,7 +41925,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42004,7 +42004,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42083,7 +42083,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42162,7 +42162,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42241,7 +42241,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42478,7 +42478,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42557,7 +42557,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42636,7 +42636,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42715,7 +42715,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42794,7 +42794,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42873,7 +42873,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42952,7 +42952,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43031,7 +43031,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43110,7 +43110,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43189,7 +43189,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43268,7 +43268,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43347,7 +43347,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43426,7 +43426,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43505,7 +43505,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43584,7 +43584,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43663,7 +43663,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43742,7 +43742,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43821,7 +43821,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43900,7 +43900,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43979,7 +43979,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44058,7 +44058,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44137,7 +44137,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44216,7 +44216,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44295,7 +44295,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44374,7 +44374,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44453,7 +44453,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44532,7 +44532,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44611,7 +44611,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44690,7 +44690,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44769,7 +44769,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44848,7 +44848,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44927,7 +44927,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45006,7 +45006,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45085,7 +45085,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45164,7 +45164,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45243,7 +45243,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45322,7 +45322,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45401,7 +45401,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45480,7 +45480,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45559,7 +45559,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45638,7 +45638,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45717,7 +45717,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45796,7 +45796,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45954,7 +45954,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46033,7 +46033,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46112,7 +46112,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46191,7 +46191,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46270,7 +46270,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46349,7 +46349,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46428,7 +46428,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46507,7 +46507,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46586,7 +46586,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46665,7 +46665,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46744,7 +46744,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46823,7 +46823,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46902,7 +46902,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46981,7 +46981,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47060,7 +47060,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47139,7 +47139,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47218,7 +47218,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47303,7 +47303,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_externo.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q600"/>
+  <dimension ref="A1:Q601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="N57" s="5" t="n">
-        <v>2501000000</v>
+        <v>2466000000</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="N58" s="5" t="n">
-        <v>-255000000</v>
+        <v>-224000000</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4796,7 +4796,7 @@
         </is>
       </c>
       <c r="N59" s="5" t="n">
-        <v>3307000000</v>
+        <v>3376000000</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="N60" s="5" t="n">
-        <v>217000000</v>
+        <v>420000000</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="N61" s="5" t="n">
-        <v>4536000000</v>
+        <v>4396000000</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="N62" s="5" t="n">
-        <v>2586000000</v>
+        <v>2733000000</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="N63" s="5" t="n">
-        <v>1560000000</v>
+        <v>1902000000</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="N64" s="5" t="n">
-        <v>2328000000</v>
+        <v>2321000000</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="N65" s="5" t="n">
-        <v>2051000000</v>
+        <v>2766000000</v>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="N66" s="5" t="n">
-        <v>-163000000</v>
+        <v>213000000</v>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="N67" s="5" t="n">
-        <v>1469000000</v>
+        <v>754000000</v>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="N68" s="5" t="n">
-        <v>2416000000</v>
+        <v>1200000000</v>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="N69" s="5" t="n">
-        <v>2250000000</v>
+        <v>665000000</v>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="N70" s="5" t="n">
-        <v>1034000000</v>
+        <v>1049000000</v>
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="N71" s="5" t="n">
-        <v>2603000000</v>
+        <v>-18000000</v>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5822,7 +5822,9 @@
           <t>Inversión extranjera directa neta emitida</t>
         </is>
       </c>
-      <c r="N72" s="4" t="n"/>
+      <c r="N72" s="5" t="n">
+        <v>277000000</v>
+      </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -5830,7 +5832,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5907,7 +5909,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5984,7 +5986,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6061,7 +6063,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6138,7 +6140,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6215,7 +6217,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6292,7 +6294,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6369,7 +6371,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6446,7 +6448,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6523,7 +6525,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6600,7 +6602,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6679,7 +6681,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6758,7 +6760,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6837,7 +6839,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6916,7 +6918,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6995,7 +6997,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7074,7 +7076,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7153,7 +7155,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7232,7 +7234,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7311,7 +7313,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7390,7 +7392,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7469,7 +7471,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7548,7 +7550,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7627,7 +7629,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7706,7 +7708,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7785,7 +7787,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7864,7 +7866,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7943,7 +7945,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8022,7 +8024,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8101,7 +8103,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8180,7 +8182,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8259,7 +8261,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8338,7 +8340,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8417,7 +8419,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8496,7 +8498,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8575,7 +8577,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8654,7 +8656,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8733,7 +8735,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8812,7 +8814,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8891,7 +8893,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8970,7 +8972,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9049,7 +9051,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9128,7 +9130,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9207,7 +9209,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9286,7 +9288,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9365,7 +9367,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9444,7 +9446,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9523,7 +9525,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9593,7 +9595,7 @@
         </is>
       </c>
       <c r="N120" s="5" t="n">
-        <v>13464000000</v>
+        <v>13462000000</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
@@ -9602,7 +9604,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9672,7 +9674,7 @@
         </is>
       </c>
       <c r="N121" s="5" t="n">
-        <v>31297000000</v>
+        <v>31298000000</v>
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
@@ -9681,7 +9683,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9751,7 +9753,7 @@
         </is>
       </c>
       <c r="N122" s="5" t="n">
-        <v>429000000</v>
+        <v>192000000</v>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
@@ -9760,7 +9762,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9830,7 +9832,7 @@
         </is>
       </c>
       <c r="N123" s="5" t="n">
-        <v>5585000000</v>
+        <v>4260000000</v>
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
@@ -9839,7 +9841,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9909,7 +9911,7 @@
         </is>
       </c>
       <c r="N124" s="5" t="n">
-        <v>16342000000</v>
+        <v>16242000000</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
@@ -9918,7 +9920,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9988,7 +9990,7 @@
         </is>
       </c>
       <c r="N125" s="5" t="n">
-        <v>2586000000</v>
+        <v>2543000000</v>
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
@@ -9997,7 +9999,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10067,7 +10069,7 @@
         </is>
       </c>
       <c r="N126" s="5" t="n">
-        <v>4604000000</v>
+        <v>4357000000</v>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
@@ -10076,7 +10078,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10146,7 +10148,7 @@
         </is>
       </c>
       <c r="N127" s="5" t="n">
-        <v>4919000000</v>
+        <v>6190000000</v>
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
@@ -10155,7 +10157,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10225,7 +10227,7 @@
         </is>
       </c>
       <c r="N128" s="5" t="n">
-        <v>-16051000000</v>
+        <v>-11812000000</v>
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
@@ -10234,7 +10236,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10304,7 +10306,7 @@
         </is>
       </c>
       <c r="N129" s="5" t="n">
-        <v>-3870000000</v>
+        <v>-2469000000</v>
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
@@ -10313,7 +10315,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10382,7 +10384,9 @@
           <t>Balanza por cuenta corriente en dólares corrientes</t>
         </is>
       </c>
-      <c r="N130" s="4" t="n"/>
+      <c r="N130" s="5" t="n">
+        <v>4463000000</v>
+      </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10390,7 +10394,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10459,7 +10463,9 @@
           <t>Balanza por cuenta corriente en dólares corrientes</t>
         </is>
       </c>
-      <c r="N131" s="4" t="n"/>
+      <c r="N131" s="5" t="n">
+        <v>13602000000</v>
+      </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10467,7 +10473,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10536,7 +10542,9 @@
           <t>Balanza por cuenta corriente en dólares corrientes</t>
         </is>
       </c>
-      <c r="N132" s="4" t="n"/>
+      <c r="N132" s="5" t="n">
+        <v>1254000000</v>
+      </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10544,7 +10552,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10613,7 +10621,9 @@
           <t>Balanza por cuenta corriente en dólares corrientes</t>
         </is>
       </c>
-      <c r="N133" s="4" t="n"/>
+      <c r="N133" s="5" t="n">
+        <v>-8574000000</v>
+      </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10621,7 +10631,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10690,7 +10700,9 @@
           <t>Balanza por cuenta corriente en dólares corrientes</t>
         </is>
       </c>
-      <c r="N134" s="4" t="n"/>
+      <c r="N134" s="5" t="n">
+        <v>-1938000000</v>
+      </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10698,7 +10710,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10767,7 +10779,9 @@
           <t>Balanza por cuenta corriente en dólares corrientes</t>
         </is>
       </c>
-      <c r="N135" s="4" t="n"/>
+      <c r="N135" s="5" t="n">
+        <v>1982000000</v>
+      </c>
       <c r="O135" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10775,7 +10789,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10844,7 +10858,9 @@
           <t>Balanza por cuenta corriente en dólares corrientes</t>
         </is>
       </c>
-      <c r="N136" s="4" t="n"/>
+      <c r="N136" s="5" t="n">
+        <v>637000000</v>
+      </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10852,7 +10868,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10921,7 +10937,9 @@
           <t>Balanza por cuenta corriente en dólares corrientes</t>
         </is>
       </c>
-      <c r="N137" s="4" t="n"/>
+      <c r="N137" s="5" t="n">
+        <v>2354000000</v>
+      </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -10929,7 +10947,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10998,7 +11016,9 @@
           <t>Balanza por cuenta corriente en dólares corrientes</t>
         </is>
       </c>
-      <c r="N138" s="4" t="n"/>
+      <c r="N138" s="5" t="n">
+        <v>569000000</v>
+      </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -11006,7 +11026,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11083,7 +11103,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11160,7 +11180,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11237,7 +11257,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11314,7 +11334,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11391,7 +11411,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11468,7 +11488,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11545,7 +11565,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11622,7 +11642,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11699,7 +11719,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11776,7 +11796,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11855,7 +11875,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11934,7 +11954,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12013,7 +12033,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12092,7 +12112,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12171,7 +12191,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12250,7 +12270,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12329,7 +12349,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12408,7 +12428,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12487,7 +12507,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12566,7 +12586,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12645,7 +12665,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12724,7 +12744,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12803,7 +12823,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12882,7 +12902,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12961,7 +12981,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13040,7 +13060,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13119,7 +13139,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13198,7 +13218,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13277,7 +13297,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13356,7 +13376,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13435,7 +13455,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13514,7 +13534,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13593,7 +13613,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13672,7 +13692,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13751,7 +13771,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13830,7 +13850,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13909,7 +13929,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13988,7 +14008,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14067,7 +14087,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14146,7 +14166,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14225,7 +14245,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14304,7 +14324,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14383,7 +14403,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14462,7 +14482,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14541,7 +14561,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14620,7 +14640,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14699,7 +14719,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14778,7 +14798,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14857,7 +14877,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14927,7 +14947,7 @@
         </is>
       </c>
       <c r="N188" s="5" t="n">
-        <v>-1137000000</v>
+        <v>-1323000000</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
@@ -14936,7 +14956,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15006,7 +15026,7 @@
         </is>
       </c>
       <c r="N189" s="5" t="n">
-        <v>1583000000</v>
+        <v>2211000000</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
@@ -15015,7 +15035,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15085,7 +15105,7 @@
         </is>
       </c>
       <c r="N190" s="5" t="n">
-        <v>5855000000</v>
+        <v>6571000000</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
@@ -15094,7 +15114,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15164,7 +15184,7 @@
         </is>
       </c>
       <c r="N191" s="5" t="n">
-        <v>4986000000</v>
+        <v>4961000000</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
@@ -15173,7 +15193,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15243,7 +15263,7 @@
         </is>
       </c>
       <c r="N192" s="5" t="n">
-        <v>2145000000</v>
+        <v>3412000000</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
@@ -15252,7 +15272,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15322,7 +15342,7 @@
         </is>
       </c>
       <c r="N193" s="5" t="n">
-        <v>1135000000</v>
+        <v>1110000000</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
@@ -15331,7 +15351,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15401,7 +15421,7 @@
         </is>
       </c>
       <c r="N194" s="5" t="n">
-        <v>2956000000</v>
+        <v>2883000000</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
@@ -15410,7 +15430,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15480,7 +15500,7 @@
         </is>
       </c>
       <c r="N195" s="5" t="n">
-        <v>1587000000</v>
+        <v>1113000000</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
@@ -15489,7 +15509,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15559,7 +15579,7 @@
         </is>
       </c>
       <c r="N196" s="5" t="n">
-        <v>-299000000</v>
+        <v>-307000000</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
@@ -15568,7 +15588,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15638,7 +15658,7 @@
         </is>
       </c>
       <c r="N197" s="5" t="n">
-        <v>622000000</v>
+        <v>1337000000</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
         <is>
@@ -15647,7 +15667,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15717,7 +15737,7 @@
         </is>
       </c>
       <c r="N198" s="5" t="n">
-        <v>564000000</v>
+        <v>1579000000</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
         <is>
@@ -15726,7 +15746,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15796,7 +15816,7 @@
         </is>
       </c>
       <c r="N199" s="5" t="n">
-        <v>1504000000</v>
+        <v>-198000000</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
         <is>
@@ -15805,7 +15825,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15875,7 +15895,7 @@
         </is>
       </c>
       <c r="N200" s="5" t="n">
-        <v>1213000000</v>
+        <v>771000000</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
         <is>
@@ -15884,7 +15904,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15954,7 +15974,7 @@
         </is>
       </c>
       <c r="N201" s="5" t="n">
-        <v>2349000000</v>
+        <v>2465000000</v>
       </c>
       <c r="O201" s="4" t="inlineStr">
         <is>
@@ -15963,7 +15983,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16033,7 +16053,7 @@
         </is>
       </c>
       <c r="N202" s="5" t="n">
-        <v>13000000</v>
+        <v>-1037000000</v>
       </c>
       <c r="O202" s="4" t="inlineStr">
         <is>
@@ -16042,7 +16062,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16112,7 +16132,7 @@
         </is>
       </c>
       <c r="N203" s="5" t="n">
-        <v>1632583330</v>
+        <v>-2549000000</v>
       </c>
       <c r="O203" s="4" t="inlineStr">
         <is>
@@ -16121,7 +16141,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16190,7 +16210,9 @@
           <t>Inversión extranjera directa neta recibida</t>
         </is>
       </c>
-      <c r="N204" s="4" t="n"/>
+      <c r="N204" s="5" t="n">
+        <v>-522000000</v>
+      </c>
       <c r="O204" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -16198,7 +16220,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16275,7 +16297,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16352,7 +16374,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16429,7 +16451,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16506,7 +16528,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16583,7 +16605,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16660,7 +16682,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16737,7 +16759,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16814,7 +16836,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16891,7 +16913,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16968,7 +16990,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17045,7 +17067,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17122,7 +17144,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17199,7 +17221,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17276,7 +17298,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17353,7 +17375,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17430,7 +17452,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17507,7 +17529,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17584,7 +17606,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17661,7 +17683,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17738,7 +17760,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17815,7 +17837,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17892,7 +17914,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17969,7 +17991,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18046,7 +18068,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18123,7 +18145,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18200,7 +18222,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18277,7 +18299,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18354,7 +18376,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18431,7 +18453,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18508,7 +18530,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18585,7 +18607,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18662,7 +18684,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18739,7 +18761,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18816,7 +18838,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18893,7 +18915,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18970,7 +18992,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19047,7 +19069,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19124,7 +19146,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19201,7 +19223,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19278,7 +19300,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19355,7 +19377,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19432,7 +19454,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19509,7 +19531,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19586,7 +19608,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19663,7 +19685,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19740,7 +19762,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19817,7 +19839,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19894,7 +19916,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19971,7 +19993,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20048,7 +20070,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20125,7 +20147,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20202,7 +20224,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20279,7 +20301,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20356,7 +20378,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20433,7 +20455,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20510,7 +20532,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20587,7 +20609,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20664,7 +20686,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20741,7 +20763,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20818,7 +20840,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20895,7 +20917,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20972,7 +20994,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21049,7 +21071,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21126,7 +21148,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21203,7 +21225,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21280,7 +21302,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21357,7 +21379,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21434,7 +21456,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21511,7 +21533,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21588,7 +21610,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21665,7 +21687,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21742,7 +21764,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21819,7 +21841,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21896,7 +21918,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21973,7 +21995,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22050,7 +22072,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22127,7 +22149,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22204,7 +22226,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22281,7 +22303,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22358,7 +22380,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22435,7 +22457,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22512,7 +22534,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22589,7 +22611,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22666,7 +22688,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22743,7 +22765,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22820,7 +22842,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22897,7 +22919,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22974,7 +22996,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23051,7 +23073,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23128,7 +23150,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23205,7 +23227,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23282,7 +23304,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23359,7 +23381,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23436,7 +23458,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23513,7 +23535,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23590,7 +23612,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23667,7 +23689,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23744,7 +23766,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23821,7 +23843,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23898,7 +23920,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23975,7 +23997,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24052,7 +24074,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24129,7 +24151,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24206,7 +24228,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24283,7 +24305,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24360,7 +24382,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24437,7 +24459,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24514,7 +24536,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24591,7 +24613,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24668,7 +24690,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24745,7 +24767,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24822,7 +24844,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24899,7 +24921,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24976,7 +24998,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25053,7 +25075,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25130,7 +25152,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25207,7 +25229,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25284,7 +25306,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25361,7 +25383,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25438,7 +25460,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25515,7 +25537,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25592,7 +25614,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25669,7 +25691,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25746,7 +25768,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25823,7 +25845,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25900,7 +25922,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25977,7 +25999,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26054,7 +26076,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26131,7 +26153,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26208,7 +26230,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26285,7 +26307,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26362,7 +26384,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26441,7 +26463,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26520,7 +26542,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26599,7 +26621,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26678,7 +26700,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26757,7 +26779,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -26836,7 +26858,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -26915,7 +26937,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -26994,7 +27016,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27073,7 +27095,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27152,7 +27174,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27231,7 +27253,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27310,7 +27332,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27389,7 +27411,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27468,7 +27490,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27547,7 +27569,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27626,7 +27648,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27705,7 +27727,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27784,7 +27806,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -27863,7 +27885,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -27942,7 +27964,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28021,7 +28043,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28100,7 +28122,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28179,7 +28201,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28258,7 +28280,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28337,7 +28359,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28416,7 +28438,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28495,7 +28517,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28574,7 +28596,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28653,7 +28675,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28732,7 +28754,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -28811,7 +28833,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -28890,7 +28912,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -28969,7 +28991,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29048,7 +29070,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29127,7 +29149,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29206,7 +29228,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29285,7 +29307,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29364,7 +29386,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29443,7 +29465,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29522,7 +29544,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29601,7 +29623,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29680,7 +29702,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29759,7 +29781,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -29838,7 +29860,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -29917,7 +29939,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -29996,7 +30018,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30075,7 +30097,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30154,7 +30176,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30233,7 +30255,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30312,7 +30334,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30391,7 +30413,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30470,7 +30492,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30549,7 +30571,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30628,7 +30650,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30707,7 +30729,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -30786,7 +30808,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -30865,7 +30887,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -30944,7 +30966,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31023,7 +31045,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31102,7 +31124,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31181,7 +31203,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31260,7 +31282,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31339,7 +31361,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31418,7 +31440,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31497,7 +31519,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31576,7 +31598,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31645,9 +31667,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N403" s="6" t="n">
-        <v>30.4335631646605</v>
-      </c>
+      <c r="N403" s="4" t="n"/>
       <c r="O403" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31655,10 +31675,14 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q403" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q403" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="4" t="inlineStr">
@@ -31724,9 +31748,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N404" s="6" t="n">
-        <v>31.7155121373594</v>
-      </c>
+      <c r="N404" s="4" t="n"/>
       <c r="O404" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31734,10 +31756,14 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q404" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q404" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="4" t="inlineStr">
@@ -31803,9 +31829,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N405" s="6" t="n">
-        <v>32.6753598645216</v>
-      </c>
+      <c r="N405" s="4" t="n"/>
       <c r="O405" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31813,10 +31837,14 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q405" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q405" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
@@ -31882,9 +31910,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N406" s="6" t="n">
-        <v>32.0418815634127</v>
-      </c>
+      <c r="N406" s="4" t="n"/>
       <c r="O406" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31892,10 +31918,14 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q406" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q406" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
@@ -31961,9 +31991,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N407" s="6" t="n">
-        <v>30.1731346634116</v>
-      </c>
+      <c r="N407" s="4" t="n"/>
       <c r="O407" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -31971,10 +31999,14 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q407" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q407" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
@@ -32040,9 +32072,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N408" s="6" t="n">
-        <v>29.087936717205</v>
-      </c>
+      <c r="N408" s="4" t="n"/>
       <c r="O408" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32050,10 +32080,14 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q408" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q408" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
@@ -32119,9 +32153,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N409" s="6" t="n">
-        <v>27.6720821945541</v>
-      </c>
+      <c r="N409" s="4" t="n"/>
       <c r="O409" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32129,10 +32161,14 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q409" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q409" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="4" t="inlineStr">
@@ -32198,9 +32234,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N410" s="6" t="n">
-        <v>27.2</v>
-      </c>
+      <c r="N410" s="4" t="n"/>
       <c r="O410" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32208,10 +32242,14 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q410" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q410" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="4" t="inlineStr">
@@ -32277,9 +32315,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N411" s="6" t="n">
-        <v>25.2877865131215</v>
-      </c>
+      <c r="N411" s="4" t="n"/>
       <c r="O411" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32287,10 +32323,14 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q411" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q411" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
@@ -32356,9 +32396,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N412" s="6" t="n">
-        <v>24.4625456431087</v>
-      </c>
+      <c r="N412" s="4" t="n"/>
       <c r="O412" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32366,10 +32404,14 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q412" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q412" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
@@ -32435,9 +32477,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N413" s="6" t="n">
-        <v>23.2505526189332</v>
-      </c>
+      <c r="N413" s="4" t="n"/>
       <c r="O413" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32445,10 +32485,14 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q413" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q413" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="4" t="inlineStr">
@@ -32514,9 +32558,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N414" s="6" t="n">
-        <v>25.2333700845277</v>
-      </c>
+      <c r="N414" s="4" t="n"/>
       <c r="O414" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32524,10 +32566,14 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q414" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q414" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
@@ -32593,9 +32639,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N415" s="6" t="n">
-        <v>23.2867223830119</v>
-      </c>
+      <c r="N415" s="4" t="n"/>
       <c r="O415" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32603,10 +32647,14 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q415" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q415" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="4" t="inlineStr">
@@ -32672,9 +32720,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N416" s="6" t="n">
-        <v>28.666129714824</v>
-      </c>
+      <c r="N416" s="4" t="n"/>
       <c r="O416" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32682,10 +32728,14 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q416" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q416" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="4" t="inlineStr">
@@ -32751,9 +32801,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N417" s="6" t="n">
-        <v>42.9378797868738</v>
-      </c>
+      <c r="N417" s="4" t="n"/>
       <c r="O417" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32761,10 +32809,14 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q417" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q417" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
@@ -32830,9 +32882,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N418" s="6" t="n">
-        <v>32.8577113922336</v>
-      </c>
+      <c r="N418" s="4" t="n"/>
       <c r="O418" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32840,10 +32890,14 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q418" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q418" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
@@ -32909,9 +32963,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N419" s="6" t="n">
-        <v>29.7245825438181</v>
-      </c>
+      <c r="N419" s="4" t="n"/>
       <c r="O419" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32919,10 +32971,14 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q419" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q419" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
@@ -32988,9 +33044,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N420" s="6" t="n">
-        <v>27.0967078982184</v>
-      </c>
+      <c r="N420" s="4" t="n"/>
       <c r="O420" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -32998,10 +33052,14 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q420" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q420" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
@@ -33067,9 +33125,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N421" s="6" t="n">
-        <v>24.097775937537</v>
-      </c>
+      <c r="N421" s="4" t="n"/>
       <c r="O421" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -33077,10 +33133,14 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q421" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q421" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
@@ -33146,9 +33206,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N422" s="6" t="n">
-        <v>29.9058906213145</v>
-      </c>
+      <c r="N422" s="4" t="n"/>
       <c r="O422" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -33156,10 +33214,14 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q422" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q422" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
@@ -33225,9 +33287,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N423" s="6" t="n">
-        <v>32.6241438861373</v>
-      </c>
+      <c r="N423" s="4" t="n"/>
       <c r="O423" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -33235,10 +33295,14 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q423" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q423" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
@@ -33304,9 +33368,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N424" s="6" t="n">
-        <v>30.5023701999944</v>
-      </c>
+      <c r="N424" s="4" t="n"/>
       <c r="O424" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -33314,10 +33376,14 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q424" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q424" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
@@ -33383,9 +33449,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N425" s="6" t="n">
-        <v>25.0503659859648</v>
-      </c>
+      <c r="N425" s="4" t="n"/>
       <c r="O425" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -33393,10 +33457,14 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q425" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q425" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
@@ -33462,9 +33530,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N426" s="6" t="n">
-        <v>22.6855128540545</v>
-      </c>
+      <c r="N426" s="4" t="n"/>
       <c r="O426" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -33472,10 +33538,14 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q426" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q426" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
@@ -33541,9 +33611,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N427" s="6" t="n">
-        <v>25.0604420194633</v>
-      </c>
+      <c r="N427" s="4" t="n"/>
       <c r="O427" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -33551,10 +33619,14 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q427" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q427" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
@@ -33620,9 +33692,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N428" s="6" t="n">
-        <v>22.5496997252233</v>
-      </c>
+      <c r="N428" s="4" t="n"/>
       <c r="O428" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -33630,10 +33700,14 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q428" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q428" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
@@ -33699,9 +33773,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N429" s="6" t="n">
-        <v>19.2929480837006</v>
-      </c>
+      <c r="N429" s="4" t="n"/>
       <c r="O429" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -33709,10 +33781,14 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q429" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q429" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
@@ -33778,9 +33854,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N430" s="6" t="n">
-        <v>20.2396826057801</v>
-      </c>
+      <c r="N430" s="4" t="n"/>
       <c r="O430" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -33788,10 +33862,14 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q430" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q430" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
@@ -33857,9 +33935,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N431" s="6" t="n">
-        <v>19.9546195219648</v>
-      </c>
+      <c r="N431" s="4" t="n"/>
       <c r="O431" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -33867,10 +33943,14 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q431" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q431" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
@@ -33936,9 +34016,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N432" s="6" t="n">
-        <v>33.020834091982</v>
-      </c>
+      <c r="N432" s="4" t="n"/>
       <c r="O432" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -33946,10 +34024,14 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q432" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q432" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
@@ -34015,9 +34097,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N433" s="6" t="n">
-        <v>38.1753164731902</v>
-      </c>
+      <c r="N433" s="4" t="n"/>
       <c r="O433" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34025,10 +34105,14 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q433" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q433" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
@@ -34094,9 +34178,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N434" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N434" s="4" t="n"/>
       <c r="O434" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34104,10 +34186,14 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q434" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q434" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
@@ -34173,9 +34259,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N435" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N435" s="4" t="n"/>
       <c r="O435" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34183,10 +34267,14 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q435" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q435" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="4" t="inlineStr">
@@ -34252,9 +34340,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N436" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N436" s="4" t="n"/>
       <c r="O436" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34262,10 +34348,14 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q436" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q436" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
@@ -34331,9 +34421,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N437" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N437" s="4" t="n"/>
       <c r="O437" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34341,10 +34429,14 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q437" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q437" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
@@ -34410,9 +34502,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N438" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N438" s="4" t="n"/>
       <c r="O438" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34420,10 +34510,14 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q438" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q438" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
@@ -34489,9 +34583,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N439" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N439" s="4" t="n"/>
       <c r="O439" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34499,10 +34591,14 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q439" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q439" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
@@ -34568,9 +34664,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N440" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N440" s="4" t="n"/>
       <c r="O440" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34578,10 +34672,14 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q440" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q440" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="4" t="inlineStr">
@@ -34647,9 +34745,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N441" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N441" s="4" t="n"/>
       <c r="O441" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34657,10 +34753,14 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q441" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q441" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="4" t="inlineStr">
@@ -34726,9 +34826,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N442" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N442" s="4" t="n"/>
       <c r="O442" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34736,10 +34834,14 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q442" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q442" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="4" t="inlineStr">
@@ -34805,9 +34907,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N443" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N443" s="4" t="n"/>
       <c r="O443" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34815,10 +34915,14 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q443" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q443" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="4" t="inlineStr">
@@ -34884,9 +34988,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N444" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N444" s="4" t="n"/>
       <c r="O444" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34894,10 +34996,14 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q444" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q444" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
@@ -34963,9 +35069,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N445" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N445" s="4" t="n"/>
       <c r="O445" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -34973,10 +35077,14 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q445" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q445" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="4" t="inlineStr">
@@ -35042,9 +35150,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N446" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N446" s="4" t="n"/>
       <c r="O446" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -35052,10 +35158,14 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q446" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q446" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="4" t="inlineStr">
@@ -35121,9 +35231,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N447" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N447" s="4" t="n"/>
       <c r="O447" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -35131,10 +35239,14 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q447" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q447" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="4" t="inlineStr">
@@ -35200,9 +35312,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N448" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N448" s="4" t="n"/>
       <c r="O448" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -35210,10 +35320,14 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q448" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q448" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="4" t="inlineStr">
@@ -35279,9 +35393,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N449" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N449" s="4" t="n"/>
       <c r="O449" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -35289,10 +35401,14 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q449" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q449" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="4" t="inlineStr">
@@ -35358,9 +35474,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N450" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N450" s="4" t="n"/>
       <c r="O450" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -35368,10 +35482,14 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q450" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q450" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
@@ -35437,9 +35555,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N451" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N451" s="4" t="n"/>
       <c r="O451" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -35447,10 +35563,14 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q451" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q451" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
@@ -35516,9 +35636,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N452" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N452" s="4" t="n"/>
       <c r="O452" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -35526,10 +35644,14 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q452" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q452" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
@@ -35595,9 +35717,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N453" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N453" s="4" t="n"/>
       <c r="O453" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -35605,10 +35725,14 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q453" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q453" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="4" t="inlineStr">
@@ -35674,9 +35798,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N454" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N454" s="4" t="n"/>
       <c r="O454" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -35684,10 +35806,14 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q454" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q454" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="4" t="inlineStr">
@@ -35753,9 +35879,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N455" s="6" t="n">
-        <v>29.5953757225434</v>
-      </c>
+      <c r="N455" s="4" t="n"/>
       <c r="O455" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -35763,10 +35887,14 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q455" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q455" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="4" t="inlineStr">
@@ -35832,9 +35960,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N456" s="6" t="n">
-        <v>30.2459016393443</v>
-      </c>
+      <c r="N456" s="4" t="n"/>
       <c r="O456" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -35842,10 +35968,14 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q456" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q456" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
@@ -35911,9 +36041,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N457" s="6" t="n">
-        <v>43.4511434511435</v>
-      </c>
+      <c r="N457" s="4" t="n"/>
       <c r="O457" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -35921,10 +36049,14 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q457" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q457" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="4" t="inlineStr">
@@ -35990,9 +36122,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N458" s="6" t="n">
-        <v>40.7547169811321</v>
-      </c>
+      <c r="N458" s="4" t="n"/>
       <c r="O458" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36000,10 +36130,14 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q458" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q458" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="4" t="inlineStr">
@@ -36069,9 +36203,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N459" s="6" t="n">
-        <v>31.1977715877437</v>
-      </c>
+      <c r="N459" s="4" t="n"/>
       <c r="O459" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36079,10 +36211,14 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q459" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q459" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="4" t="inlineStr">
@@ -36148,9 +36284,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N460" s="6" t="n">
-        <v>33.3333333333333</v>
-      </c>
+      <c r="N460" s="4" t="n"/>
       <c r="O460" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36158,10 +36292,14 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q460" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q460" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
@@ -36227,9 +36365,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N461" s="6" t="n">
-        <v>42.5471249801996</v>
-      </c>
+      <c r="N461" s="4" t="n"/>
       <c r="O461" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36237,10 +36373,14 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q461" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q461" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
@@ -36306,9 +36446,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N462" s="6" t="n">
-        <v>47.195725949267</v>
-      </c>
+      <c r="N462" s="4" t="n"/>
       <c r="O462" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36316,10 +36454,14 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q462" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q462" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
@@ -36385,9 +36527,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N463" s="6" t="n">
-        <v>13.0054444362771</v>
-      </c>
+      <c r="N463" s="4" t="n"/>
       <c r="O463" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36395,10 +36535,14 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q463" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q463" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="4" t="inlineStr">
@@ -36464,9 +36608,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N464" s="6" t="n">
-        <v>15.3500529409223</v>
-      </c>
+      <c r="N464" s="4" t="n"/>
       <c r="O464" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36474,10 +36616,14 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q464" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q464" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="4" t="inlineStr">
@@ -36543,9 +36689,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N465" s="6" t="n">
-        <v>16.3490943080464</v>
-      </c>
+      <c r="N465" s="4" t="n"/>
       <c r="O465" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36553,10 +36697,14 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q465" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q465" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="4" t="inlineStr">
@@ -36622,9 +36770,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N466" s="6" t="n">
-        <v>18.0663666874328</v>
-      </c>
+      <c r="N466" s="4" t="n"/>
       <c r="O466" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36632,10 +36778,14 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q466" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q466" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="4" t="inlineStr">
@@ -36701,9 +36851,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N467" s="6" t="n">
-        <v>16.7350337150912</v>
-      </c>
+      <c r="N467" s="4" t="n"/>
       <c r="O467" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36711,10 +36859,14 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q467" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q467" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="4" t="inlineStr">
@@ -36780,9 +36932,7 @@
           <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N468" s="6" t="n">
-        <v>14.9031673538596</v>
-      </c>
+      <c r="N468" s="4" t="n"/>
       <c r="O468" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36790,10 +36940,14 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q468" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q468" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
@@ -36827,7 +36981,7 @@
         </is>
       </c>
       <c r="G469" s="5" t="n">
-        <v>1960</v>
+        <v>2026</v>
       </c>
       <c r="H469" s="4" t="inlineStr">
         <is>
@@ -36851,17 +37005,15 @@
       </c>
       <c r="L469" s="4" t="inlineStr">
         <is>
-          <t>NE.IMP.GNFS.CD</t>
+          <t>NE.EXP.GNFS.ZS</t>
         </is>
       </c>
       <c r="M469" s="4" t="inlineStr">
         <is>
-          <t>Importaciones de bienes y servicios en dólares corrientes</t>
-        </is>
-      </c>
-      <c r="N469" s="6" t="n">
-        <v>1390889414.52148</v>
-      </c>
+          <t>Exportaciones de bienes y servicios como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="N469" s="4" t="n"/>
       <c r="O469" s="4" t="inlineStr">
         <is>
           <t>Banco Mundial - World Development Indicators</t>
@@ -36869,10 +37021,14 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q469" s="4" t="n"/>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q469" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="4" t="inlineStr">
@@ -36906,7 +37062,7 @@
         </is>
       </c>
       <c r="G470" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H470" s="4" t="inlineStr">
         <is>
@@ -36939,7 +37095,7 @@
         </is>
       </c>
       <c r="N470" s="6" t="n">
-        <v>1366605304.15442</v>
+        <v>1390889414.52148</v>
       </c>
       <c r="O470" s="4" t="inlineStr">
         <is>
@@ -36948,7 +37104,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -36985,7 +37141,7 @@
         </is>
       </c>
       <c r="G471" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H471" s="4" t="inlineStr">
         <is>
@@ -37018,7 +37174,7 @@
         </is>
       </c>
       <c r="N471" s="6" t="n">
-        <v>1489969151.60413</v>
+        <v>1366605304.15442</v>
       </c>
       <c r="O471" s="4" t="inlineStr">
         <is>
@@ -37027,7 +37183,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37064,7 +37220,7 @@
         </is>
       </c>
       <c r="G472" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H472" s="4" t="inlineStr">
         <is>
@@ -37097,7 +37253,7 @@
         </is>
       </c>
       <c r="N472" s="6" t="n">
-        <v>1458861578.70202</v>
+        <v>1489969151.60413</v>
       </c>
       <c r="O472" s="4" t="inlineStr">
         <is>
@@ -37106,7 +37262,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37143,7 +37299,7 @@
         </is>
       </c>
       <c r="G473" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H473" s="4" t="inlineStr">
         <is>
@@ -37176,7 +37332,7 @@
         </is>
       </c>
       <c r="N473" s="6" t="n">
-        <v>1473655172.41379</v>
+        <v>1458861578.70202</v>
       </c>
       <c r="O473" s="4" t="inlineStr">
         <is>
@@ -37185,7 +37341,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37222,7 +37378,7 @@
         </is>
       </c>
       <c r="G474" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H474" s="4" t="inlineStr">
         <is>
@@ -37255,7 +37411,7 @@
         </is>
       </c>
       <c r="N474" s="6" t="n">
-        <v>1612822222.22222</v>
+        <v>1473655172.41379</v>
       </c>
       <c r="O474" s="4" t="inlineStr">
         <is>
@@ -37264,7 +37420,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37301,7 +37457,7 @@
         </is>
       </c>
       <c r="G475" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H475" s="4" t="inlineStr">
         <is>
@@ -37334,7 +37490,7 @@
         </is>
       </c>
       <c r="N475" s="6" t="n">
-        <v>1505288888.88889</v>
+        <v>1612822222.22222</v>
       </c>
       <c r="O475" s="4" t="inlineStr">
         <is>
@@ -37343,7 +37499,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37380,7 +37536,7 @@
         </is>
       </c>
       <c r="G476" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H476" s="4" t="inlineStr">
         <is>
@@ -37413,7 +37569,7 @@
         </is>
       </c>
       <c r="N476" s="6" t="n">
-        <v>1612822222.22222</v>
+        <v>1505288888.88889</v>
       </c>
       <c r="O476" s="4" t="inlineStr">
         <is>
@@ -37422,7 +37578,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37459,7 +37615,7 @@
         </is>
       </c>
       <c r="G477" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H477" s="4" t="inlineStr">
         <is>
@@ -37492,7 +37648,7 @@
         </is>
       </c>
       <c r="N477" s="6" t="n">
-        <v>1956888888.88889</v>
+        <v>1612822222.22222</v>
       </c>
       <c r="O477" s="4" t="inlineStr">
         <is>
@@ -37501,7 +37657,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37538,7 +37694,7 @@
         </is>
       </c>
       <c r="G478" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H478" s="4" t="inlineStr">
         <is>
@@ -37571,7 +37727,7 @@
         </is>
       </c>
       <c r="N478" s="6" t="n">
-        <v>2042888888.88889</v>
+        <v>1956888888.88889</v>
       </c>
       <c r="O478" s="4" t="inlineStr">
         <is>
@@ -37580,7 +37736,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37617,7 +37773,7 @@
         </is>
       </c>
       <c r="G479" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H479" s="4" t="inlineStr">
         <is>
@@ -37650,7 +37806,7 @@
         </is>
       </c>
       <c r="N479" s="6" t="n">
-        <v>2171911111.11111</v>
+        <v>2042888888.88889</v>
       </c>
       <c r="O479" s="4" t="inlineStr">
         <is>
@@ -37659,7 +37815,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37696,7 +37852,7 @@
         </is>
       </c>
       <c r="G480" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H480" s="4" t="inlineStr">
         <is>
@@ -37729,7 +37885,7 @@
         </is>
       </c>
       <c r="N480" s="6" t="n">
-        <v>2463204545.45455</v>
+        <v>2171911111.11111</v>
       </c>
       <c r="O480" s="4" t="inlineStr">
         <is>
@@ -37738,7 +37894,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -37775,7 +37931,7 @@
         </is>
       </c>
       <c r="G481" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H481" s="4" t="inlineStr">
         <is>
@@ -37808,7 +37964,7 @@
         </is>
       </c>
       <c r="N481" s="6" t="n">
-        <v>2793090909.09091</v>
+        <v>2463204545.45455</v>
       </c>
       <c r="O481" s="4" t="inlineStr">
         <is>
@@ -37817,7 +37973,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -37854,7 +38010,7 @@
         </is>
       </c>
       <c r="G482" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H482" s="4" t="inlineStr">
         <is>
@@ -37887,7 +38043,7 @@
         </is>
       </c>
       <c r="N482" s="6" t="n">
-        <v>3263139534.88372</v>
+        <v>2793090909.09091</v>
       </c>
       <c r="O482" s="4" t="inlineStr">
         <is>
@@ -37896,7 +38052,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -37933,7 +38089,7 @@
         </is>
       </c>
       <c r="G483" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H483" s="4" t="inlineStr">
         <is>
@@ -37966,7 +38122,7 @@
         </is>
       </c>
       <c r="N483" s="6" t="n">
-        <v>4838441860.46512</v>
+        <v>3263139534.88372</v>
       </c>
       <c r="O483" s="4" t="inlineStr">
         <is>
@@ -37975,7 +38131,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38012,7 +38168,7 @@
         </is>
       </c>
       <c r="G484" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H484" s="4" t="inlineStr">
         <is>
@@ -38045,7 +38201,7 @@
         </is>
       </c>
       <c r="N484" s="6" t="n">
-        <v>6863837209.30233</v>
+        <v>4838441860.46512</v>
       </c>
       <c r="O484" s="4" t="inlineStr">
         <is>
@@ -38054,7 +38210,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38091,7 +38247,7 @@
         </is>
       </c>
       <c r="G485" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H485" s="4" t="inlineStr">
         <is>
@@ -38124,7 +38280,7 @@
         </is>
       </c>
       <c r="N485" s="6" t="n">
-        <v>9069255813.953489</v>
+        <v>6863837209.30233</v>
       </c>
       <c r="O485" s="4" t="inlineStr">
         <is>
@@ -38133,7 +38289,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38170,7 +38326,7 @@
         </is>
       </c>
       <c r="G486" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H486" s="4" t="inlineStr">
         <is>
@@ -38203,7 +38359,7 @@
         </is>
       </c>
       <c r="N486" s="6" t="n">
-        <v>12692465116.2791</v>
+        <v>9069255813.953489</v>
       </c>
       <c r="O486" s="4" t="inlineStr">
         <is>
@@ -38212,7 +38368,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38249,7 +38405,7 @@
         </is>
       </c>
       <c r="G487" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H487" s="4" t="inlineStr">
         <is>
@@ -38282,7 +38438,7 @@
         </is>
       </c>
       <c r="N487" s="6" t="n">
-        <v>14650348837.2093</v>
+        <v>12692465116.2791</v>
       </c>
       <c r="O487" s="4" t="inlineStr">
         <is>
@@ -38291,7 +38447,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38328,7 +38484,7 @@
         </is>
       </c>
       <c r="G488" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H488" s="4" t="inlineStr">
         <is>
@@ -38361,7 +38517,7 @@
         </is>
       </c>
       <c r="N488" s="6" t="n">
-        <v>13727674418.6047</v>
+        <v>14650348837.2093</v>
       </c>
       <c r="O488" s="4" t="inlineStr">
         <is>
@@ -38370,7 +38526,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38407,7 +38563,7 @@
         </is>
       </c>
       <c r="G489" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H489" s="4" t="inlineStr">
         <is>
@@ -38440,7 +38596,7 @@
         </is>
       </c>
       <c r="N489" s="6" t="n">
-        <v>14627837209.3023</v>
+        <v>13727674418.6047</v>
       </c>
       <c r="O489" s="4" t="inlineStr">
         <is>
@@ -38449,7 +38605,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38486,7 +38642,7 @@
         </is>
       </c>
       <c r="G490" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H490" s="4" t="inlineStr">
         <is>
@@ -38519,7 +38675,7 @@
         </is>
       </c>
       <c r="N490" s="6" t="n">
-        <v>16518209302.3256</v>
+        <v>14627837209.3023</v>
       </c>
       <c r="O490" s="4" t="inlineStr">
         <is>
@@ -38528,7 +38684,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38565,7 +38721,7 @@
         </is>
       </c>
       <c r="G491" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H491" s="4" t="inlineStr">
         <is>
@@ -38598,7 +38754,7 @@
         </is>
       </c>
       <c r="N491" s="6" t="n">
-        <v>18971186046.5116</v>
+        <v>16518209302.3256</v>
       </c>
       <c r="O491" s="4" t="inlineStr">
         <is>
@@ -38607,7 +38763,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38644,7 +38800,7 @@
         </is>
       </c>
       <c r="G492" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H492" s="4" t="inlineStr">
         <is>
@@ -38677,7 +38833,7 @@
         </is>
       </c>
       <c r="N492" s="6" t="n">
-        <v>8799209302.325581</v>
+        <v>18971186046.5116</v>
       </c>
       <c r="O492" s="4" t="inlineStr">
         <is>
@@ -38686,7 +38842,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38723,7 +38879,7 @@
         </is>
       </c>
       <c r="G493" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H493" s="4" t="inlineStr">
         <is>
@@ -38756,7 +38912,7 @@
         </is>
       </c>
       <c r="N493" s="6" t="n">
-        <v>10508123515.4394</v>
+        <v>8799209302.325581</v>
       </c>
       <c r="O493" s="4" t="inlineStr">
         <is>
@@ -38765,7 +38921,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -38802,7 +38958,7 @@
         </is>
       </c>
       <c r="G494" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H494" s="4" t="inlineStr">
         <is>
@@ -38834,8 +38990,8 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N494" s="5" t="n">
-        <v>10466520000</v>
+      <c r="N494" s="6" t="n">
+        <v>10508123515.4394</v>
       </c>
       <c r="O494" s="4" t="inlineStr">
         <is>
@@ -38844,7 +39000,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -38881,7 +39037,7 @@
         </is>
       </c>
       <c r="G495" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H495" s="4" t="inlineStr">
         <is>
@@ -38913,8 +39069,8 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N495" s="6" t="n">
-        <v>11927109278.3505</v>
+      <c r="N495" s="5" t="n">
+        <v>10466520000</v>
       </c>
       <c r="O495" s="4" t="inlineStr">
         <is>
@@ -38923,7 +39079,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -38960,7 +39116,7 @@
         </is>
       </c>
       <c r="G496" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H496" s="4" t="inlineStr">
         <is>
@@ -38993,7 +39149,7 @@
         </is>
       </c>
       <c r="N496" s="6" t="n">
-        <v>10598117241.3793</v>
+        <v>11927109278.3505</v>
       </c>
       <c r="O496" s="4" t="inlineStr">
         <is>
@@ -39002,7 +39158,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39039,7 +39195,7 @@
         </is>
       </c>
       <c r="G497" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H497" s="4" t="inlineStr">
         <is>
@@ -39072,7 +39228,7 @@
         </is>
       </c>
       <c r="N497" s="6" t="n">
-        <v>15910262068.9655</v>
+        <v>10598117241.3793</v>
       </c>
       <c r="O497" s="4" t="inlineStr">
         <is>
@@ -39081,7 +39237,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39118,7 +39274,7 @@
         </is>
       </c>
       <c r="G498" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H498" s="4" t="inlineStr">
         <is>
@@ -39151,7 +39307,7 @@
         </is>
       </c>
       <c r="N498" s="6" t="n">
-        <v>8884312274.801821</v>
+        <v>15910262068.9655</v>
       </c>
       <c r="O498" s="4" t="inlineStr">
         <is>
@@ -39160,7 +39316,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39197,7 +39353,7 @@
         </is>
       </c>
       <c r="G499" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H499" s="4" t="inlineStr">
         <is>
@@ -39230,7 +39386,7 @@
         </is>
       </c>
       <c r="N499" s="6" t="n">
-        <v>9493861738.048691</v>
+        <v>8884312274.801821</v>
       </c>
       <c r="O499" s="4" t="inlineStr">
         <is>
@@ -39239,7 +39395,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39276,7 +39432,7 @@
         </is>
       </c>
       <c r="G500" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H500" s="4" t="inlineStr">
         <is>
@@ -39308,8 +39464,8 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N500" s="5" t="n">
-        <v>0</v>
+      <c r="N500" s="6" t="n">
+        <v>9493861738.048691</v>
       </c>
       <c r="O500" s="4" t="inlineStr">
         <is>
@@ -39318,7 +39474,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39355,7 +39511,7 @@
         </is>
       </c>
       <c r="G501" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H501" s="4" t="inlineStr">
         <is>
@@ -39397,7 +39553,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39434,7 +39590,7 @@
         </is>
       </c>
       <c r="G502" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H502" s="4" t="inlineStr">
         <is>
@@ -39476,7 +39632,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39513,7 +39669,7 @@
         </is>
       </c>
       <c r="G503" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H503" s="4" t="inlineStr">
         <is>
@@ -39555,7 +39711,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39592,7 +39748,7 @@
         </is>
       </c>
       <c r="G504" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H504" s="4" t="inlineStr">
         <is>
@@ -39634,7 +39790,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39671,7 +39827,7 @@
         </is>
       </c>
       <c r="G505" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H505" s="4" t="inlineStr">
         <is>
@@ -39713,7 +39869,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -39750,7 +39906,7 @@
         </is>
       </c>
       <c r="G506" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H506" s="4" t="inlineStr">
         <is>
@@ -39792,7 +39948,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -39829,7 +39985,7 @@
         </is>
       </c>
       <c r="G507" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H507" s="4" t="inlineStr">
         <is>
@@ -39871,7 +40027,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -39908,7 +40064,7 @@
         </is>
       </c>
       <c r="G508" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H508" s="4" t="inlineStr">
         <is>
@@ -39950,7 +40106,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -39987,7 +40143,7 @@
         </is>
       </c>
       <c r="G509" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H509" s="4" t="inlineStr">
         <is>
@@ -40029,7 +40185,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40066,7 +40222,7 @@
         </is>
       </c>
       <c r="G510" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H510" s="4" t="inlineStr">
         <is>
@@ -40108,7 +40264,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40145,7 +40301,7 @@
         </is>
       </c>
       <c r="G511" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H511" s="4" t="inlineStr">
         <is>
@@ -40187,7 +40343,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40224,7 +40380,7 @@
         </is>
       </c>
       <c r="G512" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H512" s="4" t="inlineStr">
         <is>
@@ -40266,7 +40422,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40303,7 +40459,7 @@
         </is>
       </c>
       <c r="G513" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H513" s="4" t="inlineStr">
         <is>
@@ -40345,7 +40501,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40382,7 +40538,7 @@
         </is>
       </c>
       <c r="G514" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H514" s="4" t="inlineStr">
         <is>
@@ -40424,7 +40580,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40461,7 +40617,7 @@
         </is>
       </c>
       <c r="G515" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H515" s="4" t="inlineStr">
         <is>
@@ -40503,7 +40659,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40540,7 +40696,7 @@
         </is>
       </c>
       <c r="G516" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H516" s="4" t="inlineStr">
         <is>
@@ -40582,7 +40738,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40619,7 +40775,7 @@
         </is>
       </c>
       <c r="G517" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H517" s="4" t="inlineStr">
         <is>
@@ -40661,7 +40817,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40698,7 +40854,7 @@
         </is>
       </c>
       <c r="G518" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H518" s="4" t="inlineStr">
         <is>
@@ -40740,7 +40896,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -40777,7 +40933,7 @@
         </is>
       </c>
       <c r="G519" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H519" s="4" t="inlineStr">
         <is>
@@ -40819,7 +40975,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -40856,7 +41012,7 @@
         </is>
       </c>
       <c r="G520" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H520" s="4" t="inlineStr">
         <is>
@@ -40898,7 +41054,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -40935,7 +41091,7 @@
         </is>
       </c>
       <c r="G521" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H521" s="4" t="inlineStr">
         <is>
@@ -40967,8 +41123,8 @@
           <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
-      <c r="N521" s="6" t="n">
-        <v>78668126778.4577</v>
+      <c r="N521" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="O521" s="4" t="inlineStr">
         <is>
@@ -40977,7 +41133,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41014,7 +41170,7 @@
         </is>
       </c>
       <c r="G522" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H522" s="4" t="inlineStr">
         <is>
@@ -41047,7 +41203,7 @@
         </is>
       </c>
       <c r="N522" s="6" t="n">
-        <v>83592737983.1543</v>
+        <v>78668126778.4577</v>
       </c>
       <c r="O522" s="4" t="inlineStr">
         <is>
@@ -41056,7 +41212,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41093,7 +41249,7 @@
         </is>
       </c>
       <c r="G523" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H523" s="4" t="inlineStr">
         <is>
@@ -41126,7 +41282,7 @@
         </is>
       </c>
       <c r="N523" s="6" t="n">
-        <v>44352366681.2494</v>
+        <v>83592737983.1543</v>
       </c>
       <c r="O523" s="4" t="inlineStr">
         <is>
@@ -41135,7 +41291,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41172,7 +41328,7 @@
         </is>
       </c>
       <c r="G524" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H524" s="4" t="inlineStr">
         <is>
@@ -41205,7 +41361,7 @@
         </is>
       </c>
       <c r="N524" s="6" t="n">
-        <v>24577347080.6935</v>
+        <v>44352366681.2494</v>
       </c>
       <c r="O524" s="4" t="inlineStr">
         <is>
@@ -41214,7 +41370,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41251,7 +41407,7 @@
         </is>
       </c>
       <c r="G525" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H525" s="4" t="inlineStr">
         <is>
@@ -41284,7 +41440,7 @@
         </is>
       </c>
       <c r="N525" s="6" t="n">
-        <v>11515036487.7869</v>
+        <v>24577347080.6935</v>
       </c>
       <c r="O525" s="4" t="inlineStr">
         <is>
@@ -41293,7 +41449,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41330,7 +41486,7 @@
         </is>
       </c>
       <c r="G526" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H526" s="4" t="inlineStr">
         <is>
@@ -41363,7 +41519,7 @@
         </is>
       </c>
       <c r="N526" s="6" t="n">
-        <v>10756686685.3221</v>
+        <v>11515036487.7869</v>
       </c>
       <c r="O526" s="4" t="inlineStr">
         <is>
@@ -41372,7 +41528,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41409,7 +41565,7 @@
         </is>
       </c>
       <c r="G527" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H527" s="4" t="inlineStr">
         <is>
@@ -41442,7 +41598,7 @@
         </is>
       </c>
       <c r="N527" s="6" t="n">
-        <v>12326332794.8304</v>
+        <v>10756686685.3221</v>
       </c>
       <c r="O527" s="4" t="inlineStr">
         <is>
@@ -41451,7 +41607,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41488,7 +41644,7 @@
         </is>
       </c>
       <c r="G528" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H528" s="4" t="inlineStr">
         <is>
@@ -41521,7 +41677,7 @@
         </is>
       </c>
       <c r="N528" s="6" t="n">
-        <v>7982721068.68012</v>
+        <v>12326332794.8304</v>
       </c>
       <c r="O528" s="4" t="inlineStr">
         <is>
@@ -41530,7 +41686,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41567,7 +41723,7 @@
         </is>
       </c>
       <c r="G529" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H529" s="4" t="inlineStr">
         <is>
@@ -41600,7 +41756,7 @@
         </is>
       </c>
       <c r="N529" s="6" t="n">
-        <v>5605400728.82019</v>
+        <v>7982721068.68012</v>
       </c>
       <c r="O529" s="4" t="inlineStr">
         <is>
@@ -41609,7 +41765,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41646,7 +41802,7 @@
         </is>
       </c>
       <c r="G530" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H530" s="4" t="inlineStr">
         <is>
@@ -41679,7 +41835,7 @@
         </is>
       </c>
       <c r="N530" s="6" t="n">
-        <v>7856090323.7093</v>
+        <v>5605400728.82019</v>
       </c>
       <c r="O530" s="4" t="inlineStr">
         <is>
@@ -41688,7 +41844,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41725,7 +41881,7 @@
         </is>
       </c>
       <c r="G531" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H531" s="4" t="inlineStr">
         <is>
@@ -41758,7 +41914,7 @@
         </is>
       </c>
       <c r="N531" s="6" t="n">
-        <v>10280104686.5588</v>
+        <v>7856090323.7093</v>
       </c>
       <c r="O531" s="4" t="inlineStr">
         <is>
@@ -41767,7 +41923,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -41804,7 +41960,7 @@
         </is>
       </c>
       <c r="G532" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H532" s="4" t="inlineStr">
         <is>
@@ -41837,7 +41993,7 @@
         </is>
       </c>
       <c r="N532" s="6" t="n">
-        <v>10266483008.9548</v>
+        <v>10280104686.5588</v>
       </c>
       <c r="O532" s="4" t="inlineStr">
         <is>
@@ -41846,7 +42002,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -41883,7 +42039,7 @@
         </is>
       </c>
       <c r="G533" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H533" s="4" t="inlineStr">
         <is>
@@ -41916,7 +42072,7 @@
         </is>
       </c>
       <c r="N533" s="6" t="n">
-        <v>11456619838.8081</v>
+        <v>10266483008.9548</v>
       </c>
       <c r="O533" s="4" t="inlineStr">
         <is>
@@ -41925,7 +42081,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -41962,7 +42118,7 @@
         </is>
       </c>
       <c r="G534" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H534" s="4" t="inlineStr">
         <is>
@@ -41995,7 +42151,7 @@
         </is>
       </c>
       <c r="N534" s="6" t="n">
-        <v>10074121350.14</v>
+        <v>11456619838.8081</v>
       </c>
       <c r="O534" s="4" t="inlineStr">
         <is>
@@ -42004,7 +42160,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42041,7 +42197,7 @@
         </is>
       </c>
       <c r="G535" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H535" s="4" t="inlineStr">
         <is>
@@ -42065,16 +42221,16 @@
       </c>
       <c r="L535" s="4" t="inlineStr">
         <is>
-          <t>NE.IMP.GNFS.ZS</t>
+          <t>NE.IMP.GNFS.CD</t>
         </is>
       </c>
       <c r="M535" s="4" t="inlineStr">
         <is>
-          <t>Importaciones de bienes y servicios como porcentaje del PIB</t>
+          <t>Importaciones de bienes y servicios en dólares corrientes</t>
         </is>
       </c>
       <c r="N535" s="6" t="n">
-        <v>18.1484944100347</v>
+        <v>10074121350.14</v>
       </c>
       <c r="O535" s="4" t="inlineStr">
         <is>
@@ -42083,7 +42239,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42120,7 +42276,7 @@
         </is>
       </c>
       <c r="G536" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H536" s="4" t="inlineStr">
         <is>
@@ -42153,7 +42309,7 @@
         </is>
       </c>
       <c r="N536" s="6" t="n">
-        <v>16.940127294257</v>
+        <v>18.1484944100347</v>
       </c>
       <c r="O536" s="4" t="inlineStr">
         <is>
@@ -42162,7 +42318,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42199,7 +42355,7 @@
         </is>
       </c>
       <c r="G537" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H537" s="4" t="inlineStr">
         <is>
@@ -42232,7 +42388,7 @@
         </is>
       </c>
       <c r="N537" s="6" t="n">
-        <v>16.9039796782388</v>
+        <v>16.940127294257</v>
       </c>
       <c r="O537" s="4" t="inlineStr">
         <is>
@@ -42241,7 +42397,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42278,7 +42434,7 @@
         </is>
       </c>
       <c r="G538" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H538" s="4" t="inlineStr">
         <is>
@@ -42311,7 +42467,7 @@
         </is>
       </c>
       <c r="N538" s="6" t="n">
-        <v>15.1826881252719</v>
+        <v>16.9039796782388</v>
       </c>
       <c r="O538" s="4" t="inlineStr">
         <is>
@@ -42320,7 +42476,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42357,7 +42513,7 @@
         </is>
       </c>
       <c r="G539" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H539" s="4" t="inlineStr">
         <is>
@@ -42390,7 +42546,7 @@
         </is>
       </c>
       <c r="N539" s="6" t="n">
-        <v>17.9880461318293</v>
+        <v>15.1826881252719</v>
       </c>
       <c r="O539" s="4" t="inlineStr">
         <is>
@@ -42399,7 +42555,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42436,7 +42592,7 @@
         </is>
       </c>
       <c r="G540" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H540" s="4" t="inlineStr">
         <is>
@@ -42469,7 +42625,7 @@
         </is>
       </c>
       <c r="N540" s="6" t="n">
-        <v>19.1369808833223</v>
+        <v>17.9880461318293</v>
       </c>
       <c r="O540" s="4" t="inlineStr">
         <is>
@@ -42478,7 +42634,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42515,7 +42671,7 @@
         </is>
       </c>
       <c r="G541" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H541" s="4" t="inlineStr">
         <is>
@@ -42548,7 +42704,7 @@
         </is>
       </c>
       <c r="N541" s="6" t="n">
-        <v>17.141917198097</v>
+        <v>19.1369808833223</v>
       </c>
       <c r="O541" s="4" t="inlineStr">
         <is>
@@ -42557,7 +42713,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42594,7 +42750,7 @@
         </is>
       </c>
       <c r="G542" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H542" s="4" t="inlineStr">
         <is>
@@ -42627,7 +42783,7 @@
         </is>
       </c>
       <c r="N542" s="6" t="n">
-        <v>17.4359159159159</v>
+        <v>17.141917198097</v>
       </c>
       <c r="O542" s="4" t="inlineStr">
         <is>
@@ -42636,7 +42792,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42673,7 +42829,7 @@
         </is>
       </c>
       <c r="G543" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H543" s="4" t="inlineStr">
         <is>
@@ -42706,7 +42862,7 @@
         </is>
       </c>
       <c r="N543" s="6" t="n">
-        <v>19.5017163104861</v>
+        <v>17.4359159159159</v>
       </c>
       <c r="O543" s="4" t="inlineStr">
         <is>
@@ -42715,7 +42871,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -42752,7 +42908,7 @@
         </is>
       </c>
       <c r="G544" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H544" s="4" t="inlineStr">
         <is>
@@ -42785,7 +42941,7 @@
         </is>
       </c>
       <c r="N544" s="6" t="n">
-        <v>19.8625845342782</v>
+        <v>19.5017163104861</v>
       </c>
       <c r="O544" s="4" t="inlineStr">
         <is>
@@ -42794,7 +42950,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -42831,7 +42987,7 @@
         </is>
       </c>
       <c r="G545" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H545" s="4" t="inlineStr">
         <is>
@@ -42864,7 +43020,7 @@
         </is>
       </c>
       <c r="N545" s="6" t="n">
-        <v>18.7863527150408</v>
+        <v>19.8625845342782</v>
       </c>
       <c r="O545" s="4" t="inlineStr">
         <is>
@@ -42873,7 +43029,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -42910,7 +43066,7 @@
         </is>
       </c>
       <c r="G546" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H546" s="4" t="inlineStr">
         <is>
@@ -42943,7 +43099,7 @@
         </is>
       </c>
       <c r="N546" s="6" t="n">
-        <v>18.9672914369717</v>
+        <v>18.7863527150408</v>
       </c>
       <c r="O546" s="4" t="inlineStr">
         <is>
@@ -42952,7 +43108,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -42989,7 +43145,7 @@
         </is>
       </c>
       <c r="G547" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H547" s="4" t="inlineStr">
         <is>
@@ -43022,7 +43178,7 @@
         </is>
       </c>
       <c r="N547" s="6" t="n">
-        <v>19.9824395954603</v>
+        <v>18.9672914369717</v>
       </c>
       <c r="O547" s="4" t="inlineStr">
         <is>
@@ -43031,7 +43187,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43068,7 +43224,7 @@
         </is>
       </c>
       <c r="G548" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H548" s="4" t="inlineStr">
         <is>
@@ -43101,7 +43257,7 @@
         </is>
       </c>
       <c r="N548" s="6" t="n">
-        <v>19.1548469004682</v>
+        <v>19.9824395954603</v>
       </c>
       <c r="O548" s="4" t="inlineStr">
         <is>
@@ -43110,7 +43266,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43147,7 +43303,7 @@
         </is>
       </c>
       <c r="G549" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H549" s="4" t="inlineStr">
         <is>
@@ -43180,7 +43336,7 @@
         </is>
       </c>
       <c r="N549" s="6" t="n">
-        <v>18.5374307250922</v>
+        <v>19.1548469004682</v>
       </c>
       <c r="O549" s="4" t="inlineStr">
         <is>
@@ -43189,7 +43345,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43226,7 +43382,7 @@
         </is>
       </c>
       <c r="G550" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H550" s="4" t="inlineStr">
         <is>
@@ -43259,7 +43415,7 @@
         </is>
       </c>
       <c r="N550" s="6" t="n">
-        <v>24.9915324560958</v>
+        <v>18.5374307250922</v>
       </c>
       <c r="O550" s="4" t="inlineStr">
         <is>
@@ -43268,7 +43424,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43305,7 +43461,7 @@
         </is>
       </c>
       <c r="G551" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H551" s="4" t="inlineStr">
         <is>
@@ -43338,7 +43494,7 @@
         </is>
       </c>
       <c r="N551" s="6" t="n">
-        <v>28.8650225011843</v>
+        <v>24.9915324560958</v>
       </c>
       <c r="O551" s="4" t="inlineStr">
         <is>
@@ -43347,7 +43503,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43384,7 +43540,7 @@
         </is>
       </c>
       <c r="G552" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H552" s="4" t="inlineStr">
         <is>
@@ -43417,7 +43573,7 @@
         </is>
       </c>
       <c r="N552" s="6" t="n">
-        <v>35.0516999987155</v>
+        <v>28.8650225011843</v>
       </c>
       <c r="O552" s="4" t="inlineStr">
         <is>
@@ -43426,7 +43582,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43463,7 +43619,7 @@
         </is>
       </c>
       <c r="G553" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H553" s="4" t="inlineStr">
         <is>
@@ -43496,7 +43652,7 @@
         </is>
       </c>
       <c r="N553" s="6" t="n">
-        <v>37.2628061043417</v>
+        <v>35.0516999987155</v>
       </c>
       <c r="O553" s="4" t="inlineStr">
         <is>
@@ -43505,7 +43661,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43542,7 +43698,7 @@
         </is>
       </c>
       <c r="G554" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H554" s="4" t="inlineStr">
         <is>
@@ -43575,7 +43731,7 @@
         </is>
       </c>
       <c r="N554" s="6" t="n">
-        <v>28.4152558282829</v>
+        <v>37.2628061043417</v>
       </c>
       <c r="O554" s="4" t="inlineStr">
         <is>
@@ -43584,7 +43740,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43621,7 +43777,7 @@
         </is>
       </c>
       <c r="G555" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H555" s="4" t="inlineStr">
         <is>
@@ -43654,7 +43810,7 @@
         </is>
       </c>
       <c r="N555" s="6" t="n">
-        <v>24.7440804717527</v>
+        <v>28.4152558282829</v>
       </c>
       <c r="O555" s="4" t="inlineStr">
         <is>
@@ -43663,7 +43819,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43700,7 +43856,7 @@
         </is>
       </c>
       <c r="G556" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H556" s="4" t="inlineStr">
         <is>
@@ -43733,7 +43889,7 @@
         </is>
       </c>
       <c r="N556" s="6" t="n">
-        <v>24.9040349499313</v>
+        <v>24.7440804717527</v>
       </c>
       <c r="O556" s="4" t="inlineStr">
         <is>
@@ -43742,7 +43898,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -43779,7 +43935,7 @@
         </is>
       </c>
       <c r="G557" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H557" s="4" t="inlineStr">
         <is>
@@ -43812,7 +43968,7 @@
         </is>
       </c>
       <c r="N557" s="6" t="n">
-        <v>28.0072304544268</v>
+        <v>24.9040349499313</v>
       </c>
       <c r="O557" s="4" t="inlineStr">
         <is>
@@ -43821,7 +43977,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -43858,7 +44014,7 @@
         </is>
       </c>
       <c r="G558" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H558" s="4" t="inlineStr">
         <is>
@@ -43891,7 +44047,7 @@
         </is>
       </c>
       <c r="N558" s="6" t="n">
-        <v>13.0250058521405</v>
+        <v>28.0072304544268</v>
       </c>
       <c r="O558" s="4" t="inlineStr">
         <is>
@@ -43900,7 +44056,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -43937,7 +44093,7 @@
         </is>
       </c>
       <c r="G559" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H559" s="4" t="inlineStr">
         <is>
@@ -43970,7 +44126,7 @@
         </is>
       </c>
       <c r="N559" s="6" t="n">
-        <v>17.552229141671</v>
+        <v>13.0250058521405</v>
       </c>
       <c r="O559" s="4" t="inlineStr">
         <is>
@@ -43979,7 +44135,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44016,7 +44172,7 @@
         </is>
       </c>
       <c r="G560" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H560" s="4" t="inlineStr">
         <is>
@@ -44049,7 +44205,7 @@
         </is>
       </c>
       <c r="N560" s="6" t="n">
-        <v>16.8908919161425</v>
+        <v>17.552229141671</v>
       </c>
       <c r="O560" s="4" t="inlineStr">
         <is>
@@ -44058,7 +44214,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44095,7 +44251,7 @@
         </is>
       </c>
       <c r="G561" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H561" s="4" t="inlineStr">
         <is>
@@ -44128,7 +44284,7 @@
         </is>
       </c>
       <c r="N561" s="6" t="n">
-        <v>19.7089776193241</v>
+        <v>16.8908919161425</v>
       </c>
       <c r="O561" s="4" t="inlineStr">
         <is>
@@ -44137,7 +44293,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44174,7 +44330,7 @@
         </is>
       </c>
       <c r="G562" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H562" s="4" t="inlineStr">
         <is>
@@ -44207,7 +44363,7 @@
         </is>
       </c>
       <c r="N562" s="6" t="n">
-        <v>22.0660634874595</v>
+        <v>19.7089776193241</v>
       </c>
       <c r="O562" s="4" t="inlineStr">
         <is>
@@ -44216,7 +44372,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44253,7 +44409,7 @@
         </is>
       </c>
       <c r="G563" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H563" s="4" t="inlineStr">
         <is>
@@ -44286,7 +44442,7 @@
         </is>
       </c>
       <c r="N563" s="6" t="n">
-        <v>26.4174156602155</v>
+        <v>22.0660634874595</v>
       </c>
       <c r="O563" s="4" t="inlineStr">
         <is>
@@ -44295,7 +44451,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44332,7 +44488,7 @@
         </is>
       </c>
       <c r="G564" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H564" s="4" t="inlineStr">
         <is>
@@ -44365,7 +44521,7 @@
         </is>
       </c>
       <c r="N564" s="6" t="n">
-        <v>20.4064856017866</v>
+        <v>26.4174156602155</v>
       </c>
       <c r="O564" s="4" t="inlineStr">
         <is>
@@ -44374,7 +44530,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44411,7 +44567,7 @@
         </is>
       </c>
       <c r="G565" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H565" s="4" t="inlineStr">
         <is>
@@ -44444,7 +44600,7 @@
         </is>
       </c>
       <c r="N565" s="6" t="n">
-        <v>19.5319009099879</v>
+        <v>20.4064856017866</v>
       </c>
       <c r="O565" s="4" t="inlineStr">
         <is>
@@ -44453,7 +44609,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44490,7 +44646,7 @@
         </is>
       </c>
       <c r="G566" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H566" s="4" t="inlineStr">
         <is>
@@ -44522,8 +44678,8 @@
           <t>Importaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N566" s="5" t="n">
-        <v>0</v>
+      <c r="N566" s="6" t="n">
+        <v>19.5319009099879</v>
       </c>
       <c r="O566" s="4" t="inlineStr">
         <is>
@@ -44532,7 +44688,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44569,7 +44725,7 @@
         </is>
       </c>
       <c r="G567" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H567" s="4" t="inlineStr">
         <is>
@@ -44611,7 +44767,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44648,7 +44804,7 @@
         </is>
       </c>
       <c r="G568" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H568" s="4" t="inlineStr">
         <is>
@@ -44690,7 +44846,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44727,7 +44883,7 @@
         </is>
       </c>
       <c r="G569" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H569" s="4" t="inlineStr">
         <is>
@@ -44769,7 +44925,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -44806,7 +44962,7 @@
         </is>
       </c>
       <c r="G570" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H570" s="4" t="inlineStr">
         <is>
@@ -44848,7 +45004,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -44885,7 +45041,7 @@
         </is>
       </c>
       <c r="G571" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H571" s="4" t="inlineStr">
         <is>
@@ -44927,7 +45083,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -44964,7 +45120,7 @@
         </is>
       </c>
       <c r="G572" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H572" s="4" t="inlineStr">
         <is>
@@ -45006,7 +45162,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45043,7 +45199,7 @@
         </is>
       </c>
       <c r="G573" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H573" s="4" t="inlineStr">
         <is>
@@ -45085,7 +45241,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45122,7 +45278,7 @@
         </is>
       </c>
       <c r="G574" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H574" s="4" t="inlineStr">
         <is>
@@ -45164,7 +45320,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45201,7 +45357,7 @@
         </is>
       </c>
       <c r="G575" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H575" s="4" t="inlineStr">
         <is>
@@ -45243,7 +45399,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45280,7 +45436,7 @@
         </is>
       </c>
       <c r="G576" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H576" s="4" t="inlineStr">
         <is>
@@ -45322,7 +45478,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45359,7 +45515,7 @@
         </is>
       </c>
       <c r="G577" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H577" s="4" t="inlineStr">
         <is>
@@ -45401,7 +45557,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45438,7 +45594,7 @@
         </is>
       </c>
       <c r="G578" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H578" s="4" t="inlineStr">
         <is>
@@ -45480,7 +45636,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45517,7 +45673,7 @@
         </is>
       </c>
       <c r="G579" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H579" s="4" t="inlineStr">
         <is>
@@ -45559,7 +45715,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45596,7 +45752,7 @@
         </is>
       </c>
       <c r="G580" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H580" s="4" t="inlineStr">
         <is>
@@ -45638,7 +45794,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45675,7 +45831,7 @@
         </is>
       </c>
       <c r="G581" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H581" s="4" t="inlineStr">
         <is>
@@ -45717,7 +45873,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -45754,7 +45910,7 @@
         </is>
       </c>
       <c r="G582" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H582" s="4" t="inlineStr">
         <is>
@@ -45796,7 +45952,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -45833,7 +45989,7 @@
         </is>
       </c>
       <c r="G583" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H583" s="4" t="inlineStr">
         <is>
@@ -45875,7 +46031,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -45912,7 +46068,7 @@
         </is>
       </c>
       <c r="G584" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H584" s="4" t="inlineStr">
         <is>
@@ -45954,7 +46110,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -45991,7 +46147,7 @@
         </is>
       </c>
       <c r="G585" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H585" s="4" t="inlineStr">
         <is>
@@ -46033,7 +46189,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46070,7 +46226,7 @@
         </is>
       </c>
       <c r="G586" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H586" s="4" t="inlineStr">
         <is>
@@ -46112,7 +46268,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46149,7 +46305,7 @@
         </is>
       </c>
       <c r="G587" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H587" s="4" t="inlineStr">
         <is>
@@ -46181,8 +46337,8 @@
           <t>Importaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N587" s="6" t="n">
-        <v>21.1560693641619</v>
+      <c r="N587" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="O587" s="4" t="inlineStr">
         <is>
@@ -46191,7 +46347,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46228,7 +46384,7 @@
         </is>
       </c>
       <c r="G588" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H588" s="4" t="inlineStr">
         <is>
@@ -46261,7 +46417,7 @@
         </is>
       </c>
       <c r="N588" s="6" t="n">
-        <v>32.3360655737705</v>
+        <v>21.1560693641619</v>
       </c>
       <c r="O588" s="4" t="inlineStr">
         <is>
@@ -46270,7 +46426,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46307,7 +46463,7 @@
         </is>
       </c>
       <c r="G589" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H589" s="4" t="inlineStr">
         <is>
@@ -46340,7 +46496,7 @@
         </is>
       </c>
       <c r="N589" s="6" t="n">
-        <v>20.6444906444906</v>
+        <v>32.3360655737705</v>
       </c>
       <c r="O589" s="4" t="inlineStr">
         <is>
@@ -46349,7 +46505,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46386,7 +46542,7 @@
         </is>
       </c>
       <c r="G590" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H590" s="4" t="inlineStr">
         <is>
@@ -46419,7 +46575,7 @@
         </is>
       </c>
       <c r="N590" s="6" t="n">
-        <v>19.622641509434</v>
+        <v>20.6444906444906</v>
       </c>
       <c r="O590" s="4" t="inlineStr">
         <is>
@@ -46428,7 +46584,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46465,7 +46621,7 @@
         </is>
       </c>
       <c r="G591" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H591" s="4" t="inlineStr">
         <is>
@@ -46498,7 +46654,7 @@
         </is>
       </c>
       <c r="N591" s="6" t="n">
-        <v>10.1949860724234</v>
+        <v>19.622641509434</v>
       </c>
       <c r="O591" s="4" t="inlineStr">
         <is>
@@ -46507,7 +46663,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46544,7 +46700,7 @@
         </is>
       </c>
       <c r="G592" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H592" s="4" t="inlineStr">
         <is>
@@ -46577,7 +46733,7 @@
         </is>
       </c>
       <c r="N592" s="6" t="n">
-        <v>9.2816091954023</v>
+        <v>10.1949860724234</v>
       </c>
       <c r="O592" s="4" t="inlineStr">
         <is>
@@ -46586,7 +46742,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46623,7 +46779,7 @@
         </is>
       </c>
       <c r="G593" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H593" s="4" t="inlineStr">
         <is>
@@ -46656,7 +46812,7 @@
         </is>
       </c>
       <c r="N593" s="6" t="n">
-        <v>12.086171392365</v>
+        <v>9.2816091954023</v>
       </c>
       <c r="O593" s="4" t="inlineStr">
         <is>
@@ -46665,7 +46821,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46702,7 +46858,7 @@
         </is>
       </c>
       <c r="G594" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H594" s="4" t="inlineStr">
         <is>
@@ -46735,7 +46891,7 @@
         </is>
       </c>
       <c r="N594" s="6" t="n">
-        <v>10.9331140492614</v>
+        <v>12.086171392365</v>
       </c>
       <c r="O594" s="4" t="inlineStr">
         <is>
@@ -46744,7 +46900,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -46781,7 +46937,7 @@
         </is>
       </c>
       <c r="G595" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H595" s="4" t="inlineStr">
         <is>
@@ -46814,7 +46970,7 @@
         </is>
       </c>
       <c r="N595" s="6" t="n">
-        <v>13.0851234650279</v>
+        <v>10.9331140492614</v>
       </c>
       <c r="O595" s="4" t="inlineStr">
         <is>
@@ -46823,7 +46979,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -46860,7 +47016,7 @@
         </is>
       </c>
       <c r="G596" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H596" s="4" t="inlineStr">
         <is>
@@ -46893,7 +47049,7 @@
         </is>
       </c>
       <c r="N596" s="6" t="n">
-        <v>13.8763343273262</v>
+        <v>13.0851234650279</v>
       </c>
       <c r="O596" s="4" t="inlineStr">
         <is>
@@ -46902,7 +47058,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -46939,7 +47095,7 @@
         </is>
       </c>
       <c r="G597" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H597" s="4" t="inlineStr">
         <is>
@@ -46972,7 +47128,7 @@
         </is>
       </c>
       <c r="N597" s="6" t="n">
-        <v>11.5489599229843</v>
+        <v>13.8763343273262</v>
       </c>
       <c r="O597" s="4" t="inlineStr">
         <is>
@@ -46981,7 +47137,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47018,7 +47174,7 @@
         </is>
       </c>
       <c r="G598" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H598" s="4" t="inlineStr">
         <is>
@@ -47051,7 +47207,7 @@
         </is>
       </c>
       <c r="N598" s="6" t="n">
-        <v>10.0280656296837</v>
+        <v>11.5489599229843</v>
       </c>
       <c r="O598" s="4" t="inlineStr">
         <is>
@@ -47060,7 +47216,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47097,7 +47253,7 @@
         </is>
       </c>
       <c r="G599" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H599" s="4" t="inlineStr">
         <is>
@@ -47130,7 +47286,7 @@
         </is>
       </c>
       <c r="N599" s="6" t="n">
-        <v>9.5023548582854</v>
+        <v>10.0280656296837</v>
       </c>
       <c r="O599" s="4" t="inlineStr">
         <is>
@@ -47139,7 +47295,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47176,52 +47332,131 @@
         </is>
       </c>
       <c r="G600" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H600" s="4" t="inlineStr">
+        <is>
+          <t>Sector externo</t>
+        </is>
+      </c>
+      <c r="I600" s="4" t="inlineStr">
+        <is>
+          <t>sector_externo</t>
+        </is>
+      </c>
+      <c r="J600" s="4" t="inlineStr">
+        <is>
+          <t>Comercio exterior</t>
+        </is>
+      </c>
+      <c r="K600" s="4" t="inlineStr">
+        <is>
+          <t>comercio_exterior</t>
+        </is>
+      </c>
+      <c r="L600" s="4" t="inlineStr">
+        <is>
+          <t>NE.IMP.GNFS.ZS</t>
+        </is>
+      </c>
+      <c r="M600" s="4" t="inlineStr">
+        <is>
+          <t>Importaciones de bienes y servicios como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="N600" s="6" t="n">
+        <v>9.5023548582854</v>
+      </c>
+      <c r="O600" s="4" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P600" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q600" s="4" t="n"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B601" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C601" s="4" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D601" s="4" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E601" s="4" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F601" s="4" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G601" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="H600" s="4" t="inlineStr">
-        <is>
-          <t>Sector externo</t>
-        </is>
-      </c>
-      <c r="I600" s="4" t="inlineStr">
-        <is>
-          <t>sector_externo</t>
-        </is>
-      </c>
-      <c r="J600" s="4" t="inlineStr">
+      <c r="H601" s="4" t="inlineStr">
+        <is>
+          <t>Sector externo</t>
+        </is>
+      </c>
+      <c r="I601" s="4" t="inlineStr">
+        <is>
+          <t>sector_externo</t>
+        </is>
+      </c>
+      <c r="J601" s="4" t="inlineStr">
         <is>
           <t>Comercio exterior</t>
         </is>
       </c>
-      <c r="K600" s="4" t="inlineStr">
+      <c r="K601" s="4" t="inlineStr">
         <is>
           <t>comercio_exterior</t>
         </is>
       </c>
-      <c r="L600" s="4" t="inlineStr">
+      <c r="L601" s="4" t="inlineStr">
         <is>
           <t>NE.IMP.GNFS.ZS</t>
         </is>
       </c>
-      <c r="M600" s="4" t="inlineStr">
+      <c r="M601" s="4" t="inlineStr">
         <is>
           <t>Importaciones de bienes y servicios como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="N600" s="6" t="n">
+      <c r="N601" s="6" t="n">
         <v>10.1083640240415</v>
       </c>
-      <c r="O600" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P600" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="Q600" s="4" t="n"/>
+      <c r="O601" s="4" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P601" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Q601" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -47303,7 +47538,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -47324,7 +47559,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
